--- a/123.xlsx
+++ b/123.xlsx
@@ -7,8 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Данные" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Итоги" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -47,8 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -460,10 +463,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>01.01.2022</t>
-        </is>
+      <c r="A2" s="1" t="n">
+        <v>44197</v>
       </c>
       <c r="B2" t="n">
         <v>850000</v>
@@ -488,10 +489,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>01.02.2022</t>
-        </is>
+      <c r="A3" s="1" t="n">
+        <v>44228</v>
       </c>
       <c r="B3" t="n">
         <v>879000</v>
@@ -516,10 +515,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>01.03.2022</t>
-        </is>
+      <c r="A4" s="1" t="n">
+        <v>44256</v>
       </c>
       <c r="B4" t="n">
         <v>908000</v>
@@ -544,10 +541,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>01.04.2022</t>
-        </is>
+      <c r="A5" s="1" t="n">
+        <v>44287</v>
       </c>
       <c r="B5" t="n">
         <v>937000</v>
@@ -572,10 +567,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>01.05.2022</t>
-        </is>
+      <c r="A6" s="1" t="n">
+        <v>44317</v>
       </c>
       <c r="B6" t="n">
         <v>938000</v>
@@ -600,10 +593,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>01.06.2022</t>
-        </is>
+      <c r="A7" s="1" t="n">
+        <v>44348</v>
       </c>
       <c r="B7" t="n">
         <v>967000</v>
@@ -628,10 +619,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>01.07.2022</t>
-        </is>
+      <c r="A8" s="1" t="n">
+        <v>44378</v>
       </c>
       <c r="B8" t="n">
         <v>996000</v>
@@ -656,10 +645,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>01.08.2022</t>
-        </is>
+      <c r="A9" s="1" t="n">
+        <v>44409</v>
       </c>
       <c r="B9" t="n">
         <v>1025000</v>
@@ -684,10 +671,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>01.09.2022</t>
-        </is>
+      <c r="A10" s="1" t="n">
+        <v>44440</v>
       </c>
       <c r="B10" t="n">
         <v>1026000</v>
@@ -712,10 +697,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>01.10.2022</t>
-        </is>
+      <c r="A11" s="1" t="n">
+        <v>44470</v>
       </c>
       <c r="B11" t="n">
         <v>1055000</v>
@@ -740,10 +723,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>01.11.2022</t>
-        </is>
+      <c r="A12" s="1" t="n">
+        <v>44501</v>
       </c>
       <c r="B12" t="n">
         <v>1084000</v>
@@ -768,10 +749,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>01.12.2022</t>
-        </is>
+      <c r="A13" s="1" t="n">
+        <v>44531</v>
       </c>
       <c r="B13" t="n">
         <v>1113000</v>
@@ -796,10 +775,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>01.01.2023</t>
-        </is>
+      <c r="A14" s="1" t="n">
+        <v>44562</v>
       </c>
       <c r="B14" t="n">
         <v>1114000</v>
@@ -824,10 +801,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>01.02.2023</t>
-        </is>
+      <c r="A15" s="1" t="n">
+        <v>44593</v>
       </c>
       <c r="B15" t="n">
         <v>1143000</v>
@@ -852,10 +827,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>01.03.2023</t>
-        </is>
+      <c r="A16" s="1" t="n">
+        <v>44621</v>
       </c>
       <c r="B16" t="n">
         <v>1172000</v>
@@ -880,10 +853,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>01.04.2023</t>
-        </is>
+      <c r="A17" s="1" t="n">
+        <v>44652</v>
       </c>
       <c r="B17" t="n">
         <v>1201000</v>
@@ -908,10 +879,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>01.05.2023</t>
-        </is>
+      <c r="A18" s="1" t="n">
+        <v>44682</v>
       </c>
       <c r="B18" t="n">
         <v>1202000</v>
@@ -936,10 +905,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>01.06.2023</t>
-        </is>
+      <c r="A19" s="1" t="n">
+        <v>44713</v>
       </c>
       <c r="B19" t="n">
         <v>1231000</v>
@@ -964,10 +931,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>01.07.2023</t>
-        </is>
+      <c r="A20" s="1" t="n">
+        <v>44743</v>
       </c>
       <c r="B20" t="n">
         <v>1260000</v>
@@ -992,10 +957,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>01.08.2023</t>
-        </is>
+      <c r="A21" s="1" t="n">
+        <v>44774</v>
       </c>
       <c r="B21" t="n">
         <v>1289000</v>
@@ -1020,10 +983,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>01.09.2023</t>
-        </is>
+      <c r="A22" s="1" t="n">
+        <v>44805</v>
       </c>
       <c r="B22" t="n">
         <v>1290000</v>
@@ -1048,10 +1009,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>01.10.2023</t>
-        </is>
+      <c r="A23" s="1" t="n">
+        <v>44835</v>
       </c>
       <c r="B23" t="n">
         <v>1319000</v>
@@ -1076,10 +1035,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>01.11.2023</t>
-        </is>
+      <c r="A24" s="1" t="n">
+        <v>44866</v>
       </c>
       <c r="B24" t="n">
         <v>1348000</v>
@@ -1104,10 +1061,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>01.12.2023</t>
-        </is>
+      <c r="A25" s="1" t="n">
+        <v>44896</v>
       </c>
       <c r="B25" t="n">
         <v>1377000</v>
@@ -1132,10 +1087,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>01.01.2024</t>
-        </is>
+      <c r="A26" s="1" t="n">
+        <v>44927</v>
       </c>
       <c r="B26" t="n">
         <v>1378000</v>
@@ -1160,10 +1113,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>01.02.2024</t>
-        </is>
+      <c r="A27" s="1" t="n">
+        <v>44958</v>
       </c>
       <c r="B27" t="n">
         <v>1407000</v>
@@ -1188,10 +1139,8 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>01.03.2024</t>
-        </is>
+      <c r="A28" s="1" t="n">
+        <v>44986</v>
       </c>
       <c r="B28" t="n">
         <v>1436000</v>
@@ -1216,10 +1165,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>01.04.2024</t>
-        </is>
+      <c r="A29" s="1" t="n">
+        <v>45017</v>
       </c>
       <c r="B29" t="n">
         <v>1465000</v>
@@ -1244,10 +1191,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>01.05.2024</t>
-        </is>
+      <c r="A30" s="1" t="n">
+        <v>45047</v>
       </c>
       <c r="B30" t="n">
         <v>1466000</v>
@@ -1272,10 +1217,8 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>01.06.2024</t>
-        </is>
+      <c r="A31" s="1" t="n">
+        <v>45078</v>
       </c>
       <c r="B31" t="n">
         <v>1495000</v>
@@ -1300,10 +1243,8 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>01.07.2024</t>
-        </is>
+      <c r="A32" s="1" t="n">
+        <v>45108</v>
       </c>
       <c r="B32" t="n">
         <v>1524000</v>
@@ -1328,10 +1269,8 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>01.08.2024</t>
-        </is>
+      <c r="A33" s="1" t="n">
+        <v>45139</v>
       </c>
       <c r="B33" t="n">
         <v>1553000</v>
@@ -1356,10 +1295,8 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>01.09.2024</t>
-        </is>
+      <c r="A34" s="1" t="n">
+        <v>45170</v>
       </c>
       <c r="B34" t="n">
         <v>1554000</v>
@@ -1384,10 +1321,8 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>01.10.2024</t>
-        </is>
+      <c r="A35" s="1" t="n">
+        <v>45200</v>
       </c>
       <c r="B35" t="n">
         <v>1583000</v>
@@ -1412,10 +1347,8 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>01.11.2024</t>
-        </is>
+      <c r="A36" s="1" t="n">
+        <v>45231</v>
       </c>
       <c r="B36" t="n">
         <v>1612000</v>
@@ -1440,10 +1373,8 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>01.12.2024</t>
-        </is>
+      <c r="A37" s="1" t="n">
+        <v>45261</v>
       </c>
       <c r="B37" t="n">
         <v>1641000</v>
@@ -1468,10 +1399,8 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>01.01.2025</t>
-        </is>
+      <c r="A38" s="1" t="n">
+        <v>45292</v>
       </c>
       <c r="B38" t="n">
         <v>1642000</v>
@@ -1496,10 +1425,8 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>01.02.2025</t>
-        </is>
+      <c r="A39" s="1" t="n">
+        <v>45323</v>
       </c>
       <c r="B39" t="n">
         <v>1671000</v>
@@ -1524,10 +1451,8 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>01.03.2025</t>
-        </is>
+      <c r="A40" s="1" t="n">
+        <v>45352</v>
       </c>
       <c r="B40" t="n">
         <v>1700000</v>
@@ -1552,10 +1477,8 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>01.04.2025</t>
-        </is>
+      <c r="A41" s="1" t="n">
+        <v>45383</v>
       </c>
       <c r="B41" t="n">
         <v>1729000</v>
@@ -1580,10 +1503,8 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>01.05.2025</t>
-        </is>
+      <c r="A42" s="1" t="n">
+        <v>45413</v>
       </c>
       <c r="B42" t="n">
         <v>1730000</v>
@@ -1608,10 +1529,8 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>01.06.2025</t>
-        </is>
+      <c r="A43" s="1" t="n">
+        <v>45444</v>
       </c>
       <c r="B43" t="n">
         <v>1759000</v>
@@ -1636,10 +1555,8 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>01.07.2025</t>
-        </is>
+      <c r="A44" s="1" t="n">
+        <v>45474</v>
       </c>
       <c r="B44" t="n">
         <v>1788000</v>
@@ -1664,10 +1581,8 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>01.08.2025</t>
-        </is>
+      <c r="A45" s="1" t="n">
+        <v>45505</v>
       </c>
       <c r="B45" t="n">
         <v>1817000</v>
@@ -1692,10 +1607,8 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>01.09.2025</t>
-        </is>
+      <c r="A46" s="1" t="n">
+        <v>45536</v>
       </c>
       <c r="B46" t="n">
         <v>1818000</v>
@@ -1720,10 +1633,8 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>01.10.2025</t>
-        </is>
+      <c r="A47" s="1" t="n">
+        <v>45566</v>
       </c>
       <c r="B47" t="n">
         <v>1847000</v>
@@ -1748,10 +1659,8 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>01.11.2025</t>
-        </is>
+      <c r="A48" s="1" t="n">
+        <v>45597</v>
       </c>
       <c r="B48" t="n">
         <v>1876000</v>
@@ -1776,10 +1685,8 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>01.12.2025</t>
-        </is>
+      <c r="A49" s="1" t="n">
+        <v>45627</v>
       </c>
       <c r="B49" t="n">
         <v>1905000</v>
@@ -1804,10 +1711,8 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>01.01.2026</t>
-        </is>
+      <c r="A50" s="1" t="n">
+        <v>45658</v>
       </c>
       <c r="B50" t="n">
         <v>1906000</v>
@@ -1832,10 +1737,8 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>01.02.2026</t>
-        </is>
+      <c r="A51" s="1" t="n">
+        <v>45689</v>
       </c>
       <c r="B51" t="n">
         <v>1935000</v>
@@ -1857,158 +1760,6 @@
       </c>
       <c r="H51" t="n">
         <v>24.85271317829458</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Название предприятия</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>ывфывфывфы</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Дата анализа</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>18.03.2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Период анализа: с</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Период анализа: по</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Целевой уровень ROS</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>10.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Уровень значимости α</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Средняя ROS</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>22.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Стандартное отклонение</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>t-статистика</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>35.81</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>p-уровень</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Вердикт гипотезы</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Не отклоняется</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Рекомендация</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Рекомендуется к инвестированию</t>
-        </is>
       </c>
     </row>
   </sheetData>
